--- a/UTCUTS/A1_Outputs/previous_version_1/A-O_Fleet_PREV1.xlsx
+++ b/UTCUTS/A1_Outputs/previous_version_1/A-O_Fleet_PREV1.xlsx
@@ -931,7 +931,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C642055F-CF3B-4114-B5BF-DC15886043E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DBB208-C79D-4741-B0E8-70700EF54110}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
